--- a/frontend/public/template_importazione_rettili.xlsx
+++ b/frontend/public/template_importazione_rettili.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Desktop\SnakeBee - PreProd\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B308811C-D6B6-4B76-A080-523B88B318E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBCADC4-1CD0-40BB-B049-F27774EDAEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="16665" windowHeight="11415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template Importazione" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="84">
   <si>
     <t>GUIDA ALL'IMPORTAZIONE RETTILI (Template Excel/CSV)</t>
   </si>
@@ -167,24 +167,6 @@
   </si>
   <si>
     <t>Testo libero (Qualsiasi annotazione)</t>
-  </si>
-  <si>
-    <t>INFORMAZIONI BASE (OBBLIGATORIE E IDENTIFICATIVE)</t>
-  </si>
-  <si>
-    <t>ANAGRAFICA &amp; STATO</t>
-  </si>
-  <si>
-    <t>ALIMENTAZIONE PROPOSTA</t>
-  </si>
-  <si>
-    <t>FINANZE E GENEALOGIA</t>
-  </si>
-  <si>
-    <t>DOCUMENTI E ATTESTAZIONI</t>
-  </si>
-  <si>
-    <t>ALTRI CAMPI OPZIONALI</t>
   </si>
   <si>
     <t>Nome</t>
@@ -302,7 +284,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,13 +328,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF9C0006"/>
       <name val="Segoe UI"/>
@@ -365,7 +340,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,24 +371,6 @@
         <bgColor rgb="FFF9F7F1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3F7A37"/>
-        <bgColor rgb="FF3F7A37"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4F9447"/>
-        <bgColor rgb="FF4F9447"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
-        <bgColor rgb="FF70AD47"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -442,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -460,7 +417,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -478,26 +435,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -800,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -820,284 +765,241 @@
     <col min="21" max="21" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:21" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="19" t="s">
+      <c r="D1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="16" t="s">
+      <c r="K1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="18" t="s">
+      <c r="B2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18" t="s">
+      <c r="C2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18" t="s">
+      <c r="D2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-    </row>
-    <row r="2" spans="1:21" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="F2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="10">
+        <v>22</v>
+      </c>
+      <c r="J2" s="9">
+        <v>7</v>
+      </c>
+      <c r="K2" s="10">
+        <v>80</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="12">
+        <v>45</v>
+      </c>
+      <c r="J3" s="6">
+        <v>10</v>
+      </c>
+      <c r="K3" s="12">
+        <v>120</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" s="12">
+        <v>250</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="10">
+        <v>30</v>
+      </c>
+      <c r="J4" s="9">
         <v>14</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="K4" s="10">
+        <v>200</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="10">
-        <v>22</v>
-      </c>
-      <c r="J3" s="9">
-        <v>7</v>
-      </c>
-      <c r="K3" s="10">
+      <c r="M4" s="10"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="12">
-        <v>45</v>
-      </c>
-      <c r="J4" s="6">
-        <v>10</v>
-      </c>
-      <c r="K4" s="12">
-        <v>120</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="M4" s="12">
-        <v>250</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="U4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="10">
-        <v>30</v>
-      </c>
-      <c r="J5" s="9">
-        <v>14</v>
-      </c>
-      <c r="K5" s="10">
-        <v>200</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>87</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="E1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1114,20 +1016,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
     </row>
     <row r="5" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1144,7 +1046,7 @@
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="20"/>
+      <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -1322,7 +1224,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D21" s="5"/>
     </row>
@@ -1334,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D22" s="5"/>
     </row>
